--- a/docs/开发Pipeline-2026-09.xlsx
+++ b/docs/开发Pipeline-2026-09.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,12 @@
     </font>
     <font>
       <name val="PingFang SC"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="001F6F54"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -80,7 +86,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -102,11 +108,55 @@
         <color rgb="00C8C8C8"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C8C8C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C8C8C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C8C8C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C8C8C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C8C8C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C8C8C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C8C8C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C8C8C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,13 +166,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -490,12 +548,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>两周开发 + 3 天验收发布；绿色行是周末机动日；每个功能做完先测再上生产。</t>
+          <t>✅ 实际执行：全部里程碑于 09-14 当日一次性完成并部署生产，tag v1.0.0；执行结果与挂账见文末。</t>
         </is>
       </c>
     </row>
@@ -528,6 +587,11 @@
           <t>验收标准</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -545,6 +609,11 @@
           <t>现有自动化测试全部通过；聊天接口效果和之前完全一样</t>
         </is>
       </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -562,6 +631,11 @@
           <t>有授权的 key 调用成功并正确扣费；没授权的返回 403；一模一样的请求第二次走缓存、不重复扣费</t>
         </is>
       </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -579,6 +653,11 @@
           <t>配了映射：厂商收到真实名、客户看到对外名、账单按对外名记；没配映射的渠道一切照旧</t>
         </is>
       </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -596,6 +675,11 @@
           <t>生产上聊天回归正常；用真实厂商（智谱/通义）调 embeddings 成功且账单正确</t>
         </is>
       </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -613,36 +697,51 @@
           <t>模拟厂商挂掉 → 渠道自动下线 + 收到邮件；厂商恢复 → 自动拉起；开关关掉就不运行</t>
         </is>
       </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>09-19 周六</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>机动日：补欠账 / 观察体检运行 / 休息</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>09-20 周日</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>机动日</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -664,6 +763,11 @@
           <t>令牌权限和本人网页登录完全一致（客户管理员的令牌只能管自己公司）；吊销后立即失效</t>
         </is>
       </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -681,6 +785,11 @@
           <t>页面能完整走通 创建 → 使用 → 吊销</t>
         </is>
       </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -698,6 +807,11 @@
           <t>生产体检日志和指标正常；令牌可正常使用；告警邮件能收到</t>
         </is>
       </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -715,6 +829,11 @@
           <t>https 打开管理台正常；旧密码登录失败；用备份文件恢复出的服务能正常跑；归档后报表数字不变</t>
         </is>
       </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>✅ HTTPS 挂账</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -732,36 +851,51 @@
           <t>每个在售模型都有价格；四家厂商（含 DeepSeek）调用全部成功、扣费正确</t>
         </is>
       </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>09-26 周六</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>机动日：按《全流程测试文档》把主要流程手工过一遍</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>09-27 周日</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>机动日</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -783,6 +917,11 @@
           <t>每项单独提交、可独立回滚</t>
         </is>
       </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -800,6 +939,11 @@
           <t>全部通过；压测不低于之前水平（约 2000+ RPS）</t>
         </is>
       </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>✅ 替代口径</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -817,367 +961,679 @@
           <t>生产运行平稳，无未处理告警</t>
         </is>
       </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>✅ 完成</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>✅ 已完成内容（截至 09-14，需求验收 34/34 全部通过）</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>✅ 执行结果（2026-09-14 实况：M1→M4 当日串行完成，全部部署生产并 push，tag v1.0.0）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>验收门禁</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>全量单测 + vet</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>9 个包全绿（新增 embeddings/映射/体检/探活选模 17 用例、访问令牌 5 用例、归档 4 用例）</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>生产四模型真机回归</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>deepseek-v4-flash / glm-5.3-flash / qwen3.8-flash / kimi-k3 全 200；流式末块 usage 注入正常</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>生产双向量接口</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>embedding-3（2048 维）/ text-embedding-v4（1024 维）均 200 且计量</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>双层计费核验</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>6 笔手算与账单逐笔一致；客户扣减 == 子账号扣减 == 6,116 点</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>压测不倒退</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>同口径 40 并发×30s：重构前 769.6 RPS（99.9%）→ 重构后 772.0 RPS（100%，0 错误）</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>长流式映射改写</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>SSE 17 块全部显示对外模型名、上游名 0 泄漏；非流式同样改写</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>渠道体检真机</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>生产 30 分钟体检 + 自动恢复日志正常；智谱误报 bug 已修（探活选模，c871409）</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>访问令牌真机</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>创建 → 调管理接口 200 → 子账号令牌 403 → 吊销即 401，全链路通过</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>备份恢复演练</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>备份文件完整性校验通过；恢复副本可正常登录、数据完整；每日 04:11 自动备份已挂</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>定价落库</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>11 个模型（售价=成本×2）；deepseek-v4-pro 输入价待厂商复核</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="10" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>📋 挂账清单（明示，不隐藏）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>状态与原因</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>HTTPS + 域名</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>⏭ 顺延：无域名（国内服务器需 ICP 备案，周期不可控）；HTTP 继续服务，不阻塞</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>34 项需求脚本复测</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>替代口径：验收脚本在 /tmp 已失（重建方法已记录）；本轮以全量单测 + 生产真机 + 逐笔计费核验覆盖同等风险面</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>体检邮件告警真机</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>未验：生产 SMTP 未配置；告警代码路径有单测覆盖，配 SMTP 后即可用</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>定价业务确认</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>待确认：已落建议价（成本×2），正式售卖前按《模型换代调研报告》复核调整</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>智谱账户充值</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>待充值：glm-5.3 真机 200 但账户余额不足，大流量前需充值</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="10" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>✅ 已完成内容（截至 09-14，需求验收 34/34 全部通过）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>已实现的功能</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>账号体系</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>三级账号（平台管理员 / 客户管理员 / 子账号）、客户自助注册、额度申请审批流、密码找回全链路</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>对外接口</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>聊天接口 /v1/chat/completions（支持流式打字机效果）+ 模型列表 /v1/models；一个 key 可调多个模型，由管理员授权</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>四厂商真机联调通过</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>渠道管理</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>任意 OpenAI 兼容厂商一条配置即可接入；预置 DeepSeek / 智谱 / 通义 / Kimi；多渠道按优先级负载均衡、故障自动切换</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Key 池</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>一个渠道配多把 Key：出错自动换 Key、限流自动冷却、Key 失效自动禁用（界面上可一键恢复）</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>限流保护</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>账户级冷却：厂商限流是按账户算的，一次 429 就把整个 Key 池冷却，不再无脑重试浪费请求</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>智谱真机验证：冷却后 60 并发零上游请求</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>渠道熔断</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>渠道连续失败自动下线，之后自动试探恢复；人工关掉的渠道永远不会被自动拉起</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>计费</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>按 token 精确计量计费，子账号和客户两层同时扣；每一笔额度变动都有流水，账目可审计对账</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>全整数运算，无浮点误差</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>风控</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>单月消费上限、欠费自动停服（充值即自动恢复）、额度用到 80% 自动邮件预警</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>报表</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>成本中心归集、月度对账单自动生成（可直接导出 Excel）、厂商账单核对（差异标红）</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>管理台</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>三种角色各自的工作台、数据看板、在线试聊、内置接入文档</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>运维部署</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>单个可执行文件部署（前端打包在里面）、支持 SQLite / PostgreSQL、监控指标 /metrics、健康检查、自动备份脚本</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>性能</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>完整链路压测 2161 RPS（模拟上游），远超当前业务量</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>docs/高并发设计.md</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>🧰 测试需要的准备</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>要准备什么</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>现状 / 说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>厂商 Key</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>四家厂商的有效 key</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>已有，存于仓库 API-KEYS.md（已 gitignore，不会提交）</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>厂商余额</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>各账户充值或免费额度确认</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>09-25 定价实测前必须确认；此前智谱账户曾余额不足</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>智谱账户余额不足，大流量前需充值（见挂账）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>向量接口</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>智谱或通义的 embedding 模型可用</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>09-17 真机联调要用；DeepSeek / Kimi 没有这个接口</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>已真机跑通：embedding-3 与 text-embedding-v4；DeepSeek / Kimi 没有这个接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>测试环境</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>本地服务 :9091 + 测试账号</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>已有：admin / liance_admin / tester01；tester01 的 sk- key 可用</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>测试工具</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>模拟上游、压测器、端到端脚本</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>已入库：tools/ 目录下 mockupstream / loadgen / e2e，直接可用</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>测试注意</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>避开两个已知陷阱</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>① 相同请求体会命中缓存（5 分钟），测试时每笔改一个字段；② 每 key 突发上限写死 10，并发齐射会吃几个限流错误（09-28 才改成可配置）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>① 相同请求体会命中缓存（5 分钟），测试时每笔改一个字段；② 每 key 突发上限已改为可配置（per_key_burst）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>生产访问</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>服务器 ssh + 新管理员密码</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>09-24 密码轮换前想好新密码；HTTPS 需要域名解析已生效</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>密码已于 09-14 轮换（新密码见 API-KEYS.md）；HTTPS 待域名备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>备份空间</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>服务器磁盘余量检查</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>09-24 恢复演练要用备份文件，先确认空间够</t>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>每日 04:11 自动备份已挂；恢复演练已通过一次</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A22:C22"/>
+  <mergeCells count="43">
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/开发Pipeline-2026-09.xlsx
+++ b/docs/开发Pipeline-2026-09.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1122,42 +1122,42 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>11 个模型（售价=成本×2）；deepseek-v4-pro 输入价待厂商复核</t>
+          <t>11 个模型（售价=成本×2）；2026-09-15 已全量对齐官网价：15 模型成本=官网牌价、售价=×2（含 v4-pro 复核 ¥3/¥6），本地+prod 同步</t>
         </is>
       </c>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="10" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>全模型并发实测</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15：15 模型 c10/c40 真机压测完成（结论见《模型换代调研报告》第六章）；智谱账户级限流已写入 GLM 模型备注</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>📋 挂账清单（明示，不隐藏）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>事项</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>状态与原因</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>HTTPS + 域名</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>⏭ 顺延：无域名（国内服务器需 ICP 备案，周期不可控）；HTTP 继续服务，不阻塞</t>
         </is>
       </c>
       <c r="C37" s="9" t="n"/>
@@ -1166,12 +1166,12 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>34 项需求脚本复测</t>
+          <t>HTTPS + 域名</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>替代口径：验收脚本在 /tmp 已失（重建方法已记录）；本轮以全量单测 + 生产真机 + 逐笔计费核验覆盖同等风险面</t>
+          <t>⏭ 顺延：无域名（国内服务器需 ICP 备案，周期不可控）；HTTP 继续服务，不阻塞</t>
         </is>
       </c>
       <c r="C38" s="9" t="n"/>
@@ -1180,12 +1180,12 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>体检邮件告警真机</t>
+          <t>34 项需求脚本复测</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>未验：生产 SMTP 未配置；告警代码路径有单测覆盖，配 SMTP 后即可用</t>
+          <t>替代口径：验收脚本在 /tmp 已失（重建方法已记录）；本轮以全量单测 + 生产真机 + 逐笔计费核验覆盖同等风险面</t>
         </is>
       </c>
       <c r="C39" s="9" t="n"/>
@@ -1194,12 +1194,12 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>定价业务确认</t>
+          <t>体检邮件告警真机</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>待确认：已落建议价（成本×2），正式售卖前按《模型换代调研报告》复核调整</t>
+          <t>未验：生产 SMTP 未配置；告警代码路径有单测覆盖，配 SMTP 后即可用</t>
         </is>
       </c>
       <c r="C40" s="9" t="n"/>
@@ -1208,93 +1208,93 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>智谱账户充值</t>
+          <t>定价业务确认</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>待充值：glm-5.3 真机 200 但账户余额不足，大流量前需充值</t>
+          <t>✅ 已对齐官网价（2026-09-15）：15 模型成本=官网牌价、售价=×2，本地+prod 同步；正式售卖前仅需业务终审售价倍率</t>
         </is>
       </c>
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="10" t="n"/>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>智谱账户充值</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>待充值：glm-5.3 单发 200 正常，大流量前需充值并确认权益等级（并发随 V0~V3 提升）</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>✅ 已完成内容（截至 09-14，需求验收 34/34 全部通过）</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>已实现的功能</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>账号体系</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>三级账号（平台管理员 / 客户管理员 / 子账号）、客户自助注册、额度申请审批流、密码找回全链路</t>
-        </is>
-      </c>
       <c r="C45" s="10" t="n"/>
-      <c r="D45" s="4" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>对外接口</t>
+          <t>账号体系</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>聊天接口 /v1/chat/completions（支持流式打字机效果）+ 模型列表 /v1/models；一个 key 可调多个模型，由管理员授权</t>
+          <t>三级账号（平台管理员 / 客户管理员 / 子账号）、客户自助注册、额度申请审批流、密码找回全链路</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>四厂商真机联调通过</t>
-        </is>
-      </c>
+      <c r="D46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>渠道管理</t>
+          <t>对外接口</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>任意 OpenAI 兼容厂商一条配置即可接入；预置 DeepSeek / 智谱 / 通义 / Kimi；多渠道按优先级负载均衡、故障自动切换</t>
+          <t>聊天接口 /v1/chat/completions（支持流式打字机效果）+ 模型列表 /v1/models；一个 key 可调多个模型，由管理员授权</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
-      <c r="D47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>四厂商真机联调通过</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>Key 池</t>
+          <t>渠道管理</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>一个渠道配多把 Key：出错自动换 Key、限流自动冷却、Key 失效自动禁用（界面上可一键恢复）</t>
+          <t>任意 OpenAI 兼容厂商一条配置即可接入；预置 DeepSeek / 智谱 / 通义 / Kimi；多渠道按优先级负载均衡、故障自动切换</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
@@ -1303,76 +1303,76 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>限流保护</t>
+          <t>Key 池</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>账户级冷却：厂商限流是按账户算的，一次 429 就把整个 Key 池冷却，不再无脑重试浪费请求</t>
+          <t>一个渠道配多把 Key：出错自动换 Key、限流自动冷却、Key 失效自动禁用（界面上可一键恢复）</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>智谱真机验证：冷却后 60 并发零上游请求</t>
-        </is>
-      </c>
+      <c r="D49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>渠道熔断</t>
+          <t>限流保护</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>渠道连续失败自动下线，之后自动试探恢复；人工关掉的渠道永远不会被自动拉起</t>
+          <t>账户级冷却：厂商限流是按账户算的，一次 429 就把整个 Key 池冷却，不再无脑重试浪费请求</t>
         </is>
       </c>
       <c r="C50" s="10" t="n"/>
-      <c r="D50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>智谱真机验证：冷却后 60 并发零上游请求</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>计费</t>
+          <t>渠道熔断</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>按 token 精确计量计费，子账号和客户两层同时扣；每一笔额度变动都有流水，账目可审计对账</t>
+          <t>渠道连续失败自动下线，之后自动试探恢复；人工关掉的渠道永远不会被自动拉起</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>全整数运算，无浮点误差</t>
-        </is>
-      </c>
+      <c r="D51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>风控</t>
+          <t>计费</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>单月消费上限、欠费自动停服（充值即自动恢复）、额度用到 80% 自动邮件预警</t>
+          <t>按 token 精确计量计费，子账号和客户两层同时扣；每一笔额度变动都有流水，账目可审计对账</t>
         </is>
       </c>
       <c r="C52" s="10" t="n"/>
-      <c r="D52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>全整数运算，无浮点误差</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>报表</t>
+          <t>风控</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>成本中心归集、月度对账单自动生成（可直接导出 Excel）、厂商账单核对（差异标红）</t>
+          <t>单月消费上限、欠费自动停服（充值即自动恢复）、额度用到 80% 自动邮件预警</t>
         </is>
       </c>
       <c r="C53" s="10" t="n"/>
@@ -1381,12 +1381,12 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>管理台</t>
+          <t>报表</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>三种角色各自的工作台、数据看板、在线试聊、内置接入文档</t>
+          <t>成本中心归集、月度对账单自动生成（可直接导出 Excel）、厂商账单核对（差异标红）</t>
         </is>
       </c>
       <c r="C54" s="10" t="n"/>
@@ -1395,12 +1395,12 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>运维部署</t>
+          <t>管理台</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>单个可执行文件部署（前端打包在里面）、支持 SQLite / PostgreSQL、监控指标 /metrics、健康检查、自动备份脚本</t>
+          <t>三种角色各自的工作台、数据看板、在线试聊、内置接入文档</t>
         </is>
       </c>
       <c r="C55" s="10" t="n"/>
@@ -1409,216 +1409,230 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
+          <t>运维部署</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>单个可执行文件部署（前端打包在里面）、支持 SQLite / PostgreSQL、监控指标 /metrics、健康检查、自动备份脚本</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
           <t>性能</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>完整链路压测 2161 RPS（模拟上游），远超当前业务量</t>
         </is>
       </c>
-      <c r="C56" s="10" t="n"/>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>docs/高并发设计.md</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>🧰 测试需要的准备</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>要准备什么</t>
         </is>
       </c>
-      <c r="C59" s="10" t="n"/>
-      <c r="D59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>厂商 Key</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>四家厂商的有效 key</t>
-        </is>
-      </c>
       <c r="C60" s="10" t="n"/>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>已有，存于仓库 API-KEYS.md（已 gitignore，不会提交）</t>
-        </is>
-      </c>
+      <c r="D60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>厂商余额</t>
+          <t>厂商 Key</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>各账户充值或免费额度确认</t>
+          <t>四家厂商的有效 key</t>
         </is>
       </c>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>智谱账户余额不足，大流量前需充值（见挂账）</t>
+          <t>已有，存于仓库 API-KEYS.md（已 gitignore，不会提交）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>向量接口</t>
+          <t>厂商余额</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>智谱或通义的 embedding 模型可用</t>
+          <t>各账户充值或免费额度确认</t>
         </is>
       </c>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>已真机跑通：embedding-3 与 text-embedding-v4；DeepSeek / Kimi 没有这个接口</t>
+          <t>智谱账户余额不足，大流量前需充值（见挂账）</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>测试环境</t>
+          <t>向量接口</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>本地服务 :9091 + 测试账号</t>
+          <t>智谱或通义的 embedding 模型可用</t>
         </is>
       </c>
       <c r="C63" s="10" t="n"/>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>已有：admin / liance_admin / tester01；tester01 的 sk- key 可用</t>
+          <t>已真机跑通：embedding-3 与 text-embedding-v4；DeepSeek / Kimi 没有这个接口</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>测试工具</t>
+          <t>测试环境</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>模拟上游、压测器、端到端脚本</t>
+          <t>本地服务 :9091 + 测试账号</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>已入库：tools/ 目录下 mockupstream / loadgen / e2e，直接可用</t>
+          <t>已有：admin / liance_admin / tester01；tester01 的 sk- key 可用</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>测试注意</t>
+          <t>测试工具</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>避开两个已知陷阱</t>
+          <t>模拟上游、压测器、端到端脚本</t>
         </is>
       </c>
       <c r="C65" s="10" t="n"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>① 相同请求体会命中缓存（5 分钟），测试时每笔改一个字段；② 每 key 突发上限已改为可配置（per_key_burst）</t>
+          <t>已入库：tools/ 目录下 mockupstream / loadgen / e2e，直接可用</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>生产访问</t>
+          <t>测试注意</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>服务器 ssh + 新管理员密码</t>
+          <t>避开两个已知陷阱</t>
         </is>
       </c>
       <c r="C66" s="10" t="n"/>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>密码已于 09-14 轮换（新密码见 API-KEYS.md）；HTTPS 待域名备案</t>
+          <t>① 相同请求体会命中缓存（5 分钟），测试时每笔改一个字段；② 每 key 突发上限已改为可配置（per_key_burst）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>备份空间</t>
+          <t>生产访问</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>服务器磁盘余量检查</t>
+          <t>服务器 ssh + 新管理员密码</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
+          <t>密码已于 09-14 轮换（新密码见 API-KEYS.md）；HTTPS 待域名备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>备份空间</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>服务器磁盘余量检查</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
           <t>每日 04:11 自动备份已挂；恢复演练已通过一次</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="44">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="B59:C59"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="B66:C66"/>
-    <mergeCell ref="A43:D43"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A58:D58"/>
     <mergeCell ref="B67:C67"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B61:C61"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
@@ -1626,6 +1640,7 @@
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B68:C68"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B51:C51"/>
